--- a/Base_Normativa_PRC_San_Miguel.xlsx
+++ b/Base_Normativa_PRC_San_Miguel.xlsx
@@ -2,8 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Coeficientes_PRC" sheetId="1" r:id="R3687dd3725044188"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Soluciones_Muros" sheetId="2" r:id="R29f74fb4266a4923"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Coeficientes_PRC" sheetId="1" r:id="Rde9d34f911bd4bdf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Soluciones_Muros" sheetId="2" r:id="Rd83e1edf69244c68"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Soluciones_Pisos" sheetId="3" r:id="R15880d1192b54a1d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Soluciones_Techumbres" sheetId="4" r:id="R353adc7707f449a1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -216,7 +218,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="200" formatCode="0.00"/>
   </x:numFmts>
-  <x:fonts count="2">
+  <x:fonts count="4">
     <x:font>
       <x:sz val="11"/>
       <x:color theme="1"/>
@@ -228,8 +230,19 @@
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Aptos Narrow"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Aptos Narrow"/>
+    </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color rgb="FF1F2937"/>
+      <x:name val="Aptos Narrow"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="3">
+  <x:fills count="5">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -241,69 +254,62 @@
         <x:fgColor rgb="FF1E7B44"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1E7B44"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9EEF7"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="11">
+  <x:borders count="19">
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
     <x:border/>
     <x:border/>
     <x:border>
       <x:left/>
+      <x:top/>
+    </x:border>
+    <x:border>
+      <x:top/>
+    </x:border>
+    <x:border>
       <x:right/>
       <x:top/>
+    </x:border>
+    <x:border>
+      <x:left/>
+    </x:border>
+    <x:border>
+      <x:right/>
+    </x:border>
+    <x:border>
+      <x:left/>
       <x:bottom/>
     </x:border>
     <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
       <x:bottom/>
     </x:border>
     <x:border>
-      <x:left/>
       <x:right/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
       <x:bottom/>
     </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="27">
+  <x:cellXfs count="48">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -372,6 +378,59 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="3" fillId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="3" fillId="4" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -1720,7 +1779,440 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R496fcf5f6f614567"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R74c8d41f773441e6"/>
   </x:tableParts>
 </x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="22" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="22" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="22" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="22" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="22" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="22" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="22" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="22" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="22" hidden="0" customWidth="1"/>
+    <x:col min="25" max="25" width="22" hidden="0" customWidth="1"/>
+    <x:col min="26" max="26" width="34" hidden="0" customWidth="1"/>
+    <x:col min="27" max="27" width="42" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="14" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="14" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="14" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="14" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="14" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="14" hidden="0" customWidth="1"/>
+    <x:col min="18" max="18" width="14" hidden="0" customWidth="1"/>
+    <x:col min="20" max="20" width="14" hidden="0" customWidth="1"/>
+    <x:col min="21" max="21" width="14" hidden="0" customWidth="1"/>
+    <x:col min="22" max="22" width="14" hidden="0" customWidth="1"/>
+    <x:col min="23" max="23" width="14" hidden="0" customWidth="1"/>
+    <x:col min="24" max="24" width="14" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="24" hidden="0" customHeight="1">
+      <x:c r="A1" s="37" t="str">
+        <x:v>Codigo_Solucion</x:v>
+      </x:c>
+      <x:c r="B1" s="38" t="str">
+        <x:v>Elemento</x:v>
+      </x:c>
+      <x:c r="C1" s="38" t="str">
+        <x:v>Condicion_Piso</x:v>
+      </x:c>
+      <x:c r="D1" s="38" t="str">
+        <x:v>Sistema</x:v>
+      </x:c>
+      <x:c r="E1" s="38" t="str">
+        <x:v>Tipo_Referencia</x:v>
+      </x:c>
+      <x:c r="F1" s="38" t="str">
+        <x:v>Pavimento_Terminacion</x:v>
+      </x:c>
+      <x:c r="G1" s="38" t="str">
+        <x:v>Placa_Estructural</x:v>
+      </x:c>
+      <x:c r="H1" s="38" t="str">
+        <x:v>Espesor_Placa_Min_mm</x:v>
+      </x:c>
+      <x:c r="I1" s="38" t="str">
+        <x:v>Espesor_Placa_Max_mm</x:v>
+      </x:c>
+      <x:c r="J1" s="38" t="str">
+        <x:v>Estructura_Principal</x:v>
+      </x:c>
+      <x:c r="K1" s="38" t="str">
+        <x:v>Aislante</x:v>
+      </x:c>
+      <x:c r="L1" s="38" t="str">
+        <x:v>Espesor_Aislante_mm</x:v>
+      </x:c>
+      <x:c r="M1" s="38" t="str">
+        <x:v>Densidad_Aislante_kg_m3</x:v>
+      </x:c>
+      <x:c r="N1" s="38" t="str">
+        <x:v>Barrera_Humedad_Viento</x:v>
+      </x:c>
+      <x:c r="O1" s="38" t="str">
+        <x:v>Revestimiento_Inferior</x:v>
+      </x:c>
+      <x:c r="P1" s="38" t="str">
+        <x:v>Espesor_Rev_Inferior_mm</x:v>
+      </x:c>
+      <x:c r="Q1" s="38" t="str">
+        <x:v>Cama_Ripio_mm</x:v>
+      </x:c>
+      <x:c r="R1" s="38" t="str">
+        <x:v>Radier_Hormigon_mm</x:v>
+      </x:c>
+      <x:c r="S1" s="38" t="str">
+        <x:v>Aislacion_Sobrecimiento</x:v>
+      </x:c>
+      <x:c r="T1" s="38" t="str">
+        <x:v>R100_Min_Sobrecimiento</x:v>
+      </x:c>
+      <x:c r="U1" s="38" t="str">
+        <x:v>U_W_m2K</x:v>
+      </x:c>
+      <x:c r="V1" s="38" t="str">
+        <x:v>Rt_m2K_W</x:v>
+      </x:c>
+      <x:c r="W1" s="38" t="str">
+        <x:v>U_Max_Zona_D</x:v>
+      </x:c>
+      <x:c r="X1" s="38" t="str">
+        <x:v>Rt_Min_Zona_D</x:v>
+      </x:c>
+      <x:c r="Y1" s="38" t="str">
+        <x:v>Compatibilidad_Zona_D</x:v>
+      </x:c>
+      <x:c r="Z1" s="38" t="str">
+        <x:v>Fuente</x:v>
+      </x:c>
+      <x:c r="AA1" s="39" t="str">
+        <x:v>Observacion</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="60" hidden="0" customHeight="1">
+      <x:c r="A2" s="40" t="str">
+        <x:v>PST-REF-ZD</x:v>
+      </x:c>
+      <x:c r="B2" s="41" t="str">
+        <x:v>Piso</x:v>
+      </x:c>
+      <x:c r="C2" s="41" t="str">
+        <x:v>Apoyado sobre terreno</x:v>
+      </x:c>
+      <x:c r="D2" s="41" t="str">
+        <x:v>Radier de hormigón sobre terreno</x:v>
+      </x:c>
+      <x:c r="E2" s="41" t="str">
+        <x:v>Criterio constructivo de referencia + exigencia OGUC</x:v>
+      </x:c>
+      <x:c r="F2" s="41" t="str">
+        <x:v>Según recinto</x:v>
+      </x:c>
+      <x:c r="G2" s="41" t="str"/>
+      <x:c r="H2" s="46" t="str"/>
+      <x:c r="I2" s="46" t="str"/>
+      <x:c r="J2" s="41" t="str">
+        <x:v>Radier/losa apoyada directamente sobre terreno</x:v>
+      </x:c>
+      <x:c r="K2" s="41" t="str"/>
+      <x:c r="L2" s="46" t="str"/>
+      <x:c r="M2" s="46" t="str"/>
+      <x:c r="N2" s="41" t="str">
+        <x:v>No aplica</x:v>
+      </x:c>
+      <x:c r="O2" s="41" t="str">
+        <x:v>No aplica</x:v>
+      </x:c>
+      <x:c r="P2" s="46" t="str"/>
+      <x:c r="Q2" s="46" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="R2" s="46" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="S2" s="41" t="str">
+        <x:v>Aislación térmica exterior del sobrecimiento</x:v>
+      </x:c>
+      <x:c r="T2" s="46" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="U2" s="46" t="str"/>
+      <x:c r="V2" s="46" t="str"/>
+      <x:c r="W2" s="46" t="str"/>
+      <x:c r="X2" s="46" t="str"/>
+      <x:c r="Y2" s="41" t="str">
+        <x:v>Cumple si R100 ≥ 45 en el sobrecimiento</x:v>
+      </x:c>
+      <x:c r="Z2" s="41" t="str">
+        <x:v>OGUC art. 4.1.10 + criterio constructivo seleccionado en la tesis</x:v>
+      </x:c>
+      <x:c r="AA2" s="42" t="str">
+        <x:v>Ripio compactado 8 cm y radier de hormigón 10 cm se usan como referencia constructiva. Para Zona D se considera aislación térmica exterior del sobrecimiento con R100 ≥ 45. Dentro de este criterio, el radier/losa apoyado directamente sobre terreno no requiere aislación bajo su superficie.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="36" hidden="0" customHeight="1">
+      <x:c r="A3" s="43" t="str">
+        <x:v>F12-PV+LFV</x:v>
+      </x:c>
+      <x:c r="B3" s="44" t="str">
+        <x:v>Piso</x:v>
+      </x:c>
+      <x:c r="C3" s="44" t="str">
+        <x:v>Ventilado</x:v>
+      </x:c>
+      <x:c r="D3" s="44" t="str">
+        <x:v>Entramado de madera con lana de fibra de vidrio</x:v>
+      </x:c>
+      <x:c r="E3" s="44" t="str">
+        <x:v>Solución técnica MINVU F12 – PV+LFV</x:v>
+      </x:c>
+      <x:c r="F3" s="44" t="str">
+        <x:v>Según recinto</x:v>
+      </x:c>
+      <x:c r="G3" s="44" t="str">
+        <x:v>OSB</x:v>
+      </x:c>
+      <x:c r="H3" s="47" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="I3" s="47" t="n">
+        <x:v>11.1</x:v>
+      </x:c>
+      <x:c r="J3" s="44" t="str">
+        <x:v>Pino 2"x8"</x:v>
+      </x:c>
+      <x:c r="K3" s="44" t="str">
+        <x:v>Lana de fibra de vidrio</x:v>
+      </x:c>
+      <x:c r="L3" s="47" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="M3" s="47" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="N3" s="44" t="str">
+        <x:v>Barrera de humedad y viento</x:v>
+      </x:c>
+      <x:c r="O3" s="44" t="str">
+        <x:v>Fibrocemento</x:v>
+      </x:c>
+      <x:c r="P3" s="47" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="Q3" s="47" t="str"/>
+      <x:c r="R3" s="47" t="str"/>
+      <x:c r="S3" s="44" t="str"/>
+      <x:c r="T3" s="47" t="str"/>
+      <x:c r="U3" s="47" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="V3" s="47" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="W3" s="47" t="n">
+        <x:v>0.6</x:v>
+      </x:c>
+      <x:c r="X3" s="47" t="n">
+        <x:v>1.67</x:v>
+      </x:c>
+      <x:c r="Y3" s="44" t="str">
+        <x:v>Cumple</x:v>
+      </x:c>
+      <x:c r="Z3" s="44" t="str">
+        <x:v>MINVU, solución F12 – PV+LFV; sistematizada en la tesis</x:v>
+      </x:c>
+      <x:c r="AA3" s="45" t="str">
+        <x:v>Piso ventilado con placa estructural OSB aprox. 10–11,1 mm, envigado de pino 2x8, lana de fibra de vidrio 80 mm y fibrocemento inferior 10 mm.</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="36" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="22" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="22" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="22" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="22" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="22" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="22" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="22" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="22" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="22" hidden="0" customWidth="1"/>
+    <x:col min="21" max="21" width="22" hidden="0" customWidth="1"/>
+    <x:col min="22" max="22" width="32" hidden="0" customWidth="1"/>
+    <x:col min="23" max="23" width="42" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="14" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="14" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="14" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="14" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="14" hidden="0" customWidth="1"/>
+    <x:col min="18" max="18" width="14" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="14" hidden="0" customWidth="1"/>
+    <x:col min="20" max="20" width="14" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="24" hidden="0" customHeight="1">
+      <x:c r="A1" s="37" t="str">
+        <x:v>Codigo_Solucion</x:v>
+      </x:c>
+      <x:c r="B1" s="38" t="str">
+        <x:v>Elemento</x:v>
+      </x:c>
+      <x:c r="C1" s="38" t="str">
+        <x:v>Sistema</x:v>
+      </x:c>
+      <x:c r="D1" s="38" t="str">
+        <x:v>Geometria</x:v>
+      </x:c>
+      <x:c r="E1" s="38" t="str">
+        <x:v>Cielo_Interior</x:v>
+      </x:c>
+      <x:c r="F1" s="38" t="str">
+        <x:v>Espesor_Cielo_mm</x:v>
+      </x:c>
+      <x:c r="G1" s="38" t="str">
+        <x:v>Barrera_Vapor</x:v>
+      </x:c>
+      <x:c r="H1" s="38" t="str">
+        <x:v>Listoneado_Cielo</x:v>
+      </x:c>
+      <x:c r="I1" s="38" t="str">
+        <x:v>Aislante</x:v>
+      </x:c>
+      <x:c r="J1" s="38" t="str">
+        <x:v>Espesor_Aislante_mm</x:v>
+      </x:c>
+      <x:c r="K1" s="38" t="str">
+        <x:v>Densidad_Aislante_Min_kg_m3</x:v>
+      </x:c>
+      <x:c r="L1" s="38" t="str">
+        <x:v>Estructura_Principal</x:v>
+      </x:c>
+      <x:c r="M1" s="38" t="str">
+        <x:v>Separacion_Cerchas_cm</x:v>
+      </x:c>
+      <x:c r="N1" s="38" t="str">
+        <x:v>Espacio_Entretecho</x:v>
+      </x:c>
+      <x:c r="O1" s="38" t="str">
+        <x:v>Ventilacion_Entretecho</x:v>
+      </x:c>
+      <x:c r="P1" s="38" t="str">
+        <x:v>Cubierta_Exterior</x:v>
+      </x:c>
+      <x:c r="Q1" s="38" t="str">
+        <x:v>U_W_m2K</x:v>
+      </x:c>
+      <x:c r="R1" s="38" t="str">
+        <x:v>Rt_m2K_W</x:v>
+      </x:c>
+      <x:c r="S1" s="38" t="str">
+        <x:v>U_Max_Zona_D</x:v>
+      </x:c>
+      <x:c r="T1" s="38" t="str">
+        <x:v>Rt_Min_Zona_D</x:v>
+      </x:c>
+      <x:c r="U1" s="38" t="str">
+        <x:v>Compatibilidad_Zona_D</x:v>
+      </x:c>
+      <x:c r="V1" s="38" t="str">
+        <x:v>Fuente</x:v>
+      </x:c>
+      <x:c r="W1" s="39" t="str">
+        <x:v>Observacion</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="36" hidden="0" customHeight="1">
+      <x:c r="A2" s="43" t="str">
+        <x:v>1.1.G.A.1.1</x:v>
+      </x:c>
+      <x:c r="B2" s="44" t="str">
+        <x:v>Techumbre</x:v>
+      </x:c>
+      <x:c r="C2" s="44" t="str">
+        <x:v>Cerchas de madera con lana de fibra de vidrio sobre cielo horizontal</x:v>
+      </x:c>
+      <x:c r="D2" s="44" t="str">
+        <x:v>Una o más aguas</x:v>
+      </x:c>
+      <x:c r="E2" s="44" t="str">
+        <x:v>Yeso-cartón</x:v>
+      </x:c>
+      <x:c r="F2" s="47" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G2" s="44" t="str">
+        <x:v>Cuando corresponda según análisis higrotérmico</x:v>
+      </x:c>
+      <x:c r="H2" s="44" t="str">
+        <x:v>Pino</x:v>
+      </x:c>
+      <x:c r="I2" s="44" t="str">
+        <x:v>Lana de fibra de vidrio</x:v>
+      </x:c>
+      <x:c r="J2" s="47" t="n">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="K2" s="47" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="L2" s="44" t="str">
+        <x:v>Cerchas de madera</x:v>
+      </x:c>
+      <x:c r="M2" s="47" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="N2" s="44" t="str">
+        <x:v>Entretecho</x:v>
+      </x:c>
+      <x:c r="O2" s="44" t="str">
+        <x:v>Ventilación cruzada cuando corresponda</x:v>
+      </x:c>
+      <x:c r="P2" s="44" t="str">
+        <x:v>Según solución de cubierta definida para el proyecto</x:v>
+      </x:c>
+      <x:c r="Q2" s="47" t="n">
+        <x:v>0.37</x:v>
+      </x:c>
+      <x:c r="R2" s="47" t="n">
+        <x:v>2.73</x:v>
+      </x:c>
+      <x:c r="S2" s="47" t="n">
+        <x:v>0.38</x:v>
+      </x:c>
+      <x:c r="T2" s="47" t="n">
+        <x:v>2.63</x:v>
+      </x:c>
+      <x:c r="U2" s="44" t="str">
+        <x:v>Cumple</x:v>
+      </x:c>
+      <x:c r="V2" s="44" t="str">
+        <x:v>LOSCAT Edición 14, 2026 - DITEC MINVU</x:v>
+      </x:c>
+      <x:c r="W2" s="45" t="str">
+        <x:v>Solución de referencia seleccionada en la tesis para techumbre liviana. La barrera de vapor y ventilación del entretecho deben resolverse según corresponda.</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
 </file>